--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_VALENCIA BASKET.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_VALENCIA BASKET.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>296.8</v>
+        <v>369.56</v>
       </c>
       <c r="C2" t="n">
-        <v>297.6</v>
+        <v>370.24</v>
       </c>
       <c r="D2" t="n">
-        <v>118.2795698924731</v>
+        <v>116.9511668107174</v>
       </c>
       <c r="E2" t="n">
-        <v>116.9354838709677</v>
+        <v>111.2791702679343</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5567765567765568</v>
+        <v>0.5385756676557863</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1364411597498579</v>
+        <v>0.1322510032834732</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3767123287671233</v>
+        <v>0.3689839572192513</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1758241758241758</v>
+        <v>0.2077151335311573</v>
       </c>
       <c r="J2" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K2" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="L2" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="M2" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="N2" t="n">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="O2" t="n">
-        <v>137</v>
+        <v>183</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5018315018315018</v>
+        <v>0.543026706231454</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R2" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1684981684981685</v>
+        <v>0.1602373887240356</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V2" t="n">
-        <v>0.03296703296703297</v>
+        <v>0.02967359050445104</v>
       </c>
       <c r="W2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.07326007326007326</v>
+        <v>0.0830860534124629</v>
       </c>
       <c r="Z2" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AA2" t="n">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3992673992673993</v>
+        <v>0.3916913946587537</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8248175182481752</v>
+        <v>0.8142076502732241</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4130434782608696</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.25</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3394495412844037</v>
+        <v>0.3257575757575757</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.64963503649635</v>
+        <v>1.628415300546448</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.111111111111111</v>
+        <v>1.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9767441860465116</v>
+        <v>0.95625</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.851063829787234</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8727272727272727</v>
+        <v>0.8985507246376812</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.875</v>
+        <v>1.80952380952381</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.791666666666667</v>
+        <v>1.758620689655172</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.6875</v>
+        <v>5.810344827586207</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.479166666666667</v>
+        <v>7.568965517241379</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.2</v>
+        <v>73.91200000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>74.40000000000001</v>
+        <v>74.048</v>
       </c>
       <c r="D3" t="n">
-        <v>118.2795698924731</v>
+        <v>116.9511668107174</v>
       </c>
       <c r="E3" t="n">
-        <v>116.9354838709677</v>
+        <v>111.2791702679343</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5567765567765568</v>
+        <v>0.5385756676557862</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1364411597498579</v>
+        <v>0.1322510032834732</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3767123287671233</v>
+        <v>0.3689839572192513</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1758241758241758</v>
+        <v>0.2077151335311573</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="L3" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="M3" t="n">
-        <v>11.25</v>
+        <v>10.6</v>
       </c>
       <c r="N3" t="n">
-        <v>28.25</v>
+        <v>29.8</v>
       </c>
       <c r="O3" t="n">
-        <v>34.25</v>
+        <v>36.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5018315018315018</v>
+        <v>0.543026706231454</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1684981684981685</v>
+        <v>0.1602373887240356</v>
       </c>
       <c r="T3" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>0.03296703296703297</v>
+        <v>0.02967359050445104</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.07326007326007326</v>
+        <v>0.08308605341246289</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.25</v>
+        <v>8.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>27.25</v>
+        <v>26.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3992673992673993</v>
+        <v>0.3916913946587536</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8248175182481752</v>
+        <v>0.8142076502732241</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4130434782608696</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.25</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3394495412844037</v>
+        <v>0.3257575757575757</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.64963503649635</v>
+        <v>1.628415300546448</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.111111111111111</v>
+        <v>1.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9767441860465116</v>
+        <v>0.9562499999999999</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.851063829787234</v>
+        <v>0.8166666666666668</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8727272727272727</v>
+        <v>0.8985507246376812</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.875</v>
+        <v>1.809523809523809</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.791666666666667</v>
+        <v>1.758620689655172</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.6875</v>
+        <v>5.810344827586207</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.479166666666667</v>
+        <v>7.568965517241381</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>298.4</v>
+        <v>370.92</v>
       </c>
       <c r="C4" t="n">
-        <v>297.6</v>
+        <v>370.24</v>
       </c>
       <c r="D4" t="n">
-        <v>116.9354838709677</v>
+        <v>111.2791702679343</v>
       </c>
       <c r="E4" t="n">
-        <v>118.2795698924731</v>
+        <v>116.9511668107174</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5459558823529411</v>
+        <v>0.523598820058997</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1360741169658367</v>
+        <v>0.139886225869626</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3219178082191781</v>
+        <v>0.3068783068783069</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1875</v>
+        <v>0.168141592920354</v>
       </c>
       <c r="J4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K4" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="L4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M4" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="N4" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="O4" t="n">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5132743362831859</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R4" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2169117647058824</v>
+        <v>0.2005899705014749</v>
       </c>
       <c r="T4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04411764705882353</v>
+        <v>0.04129793510324484</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03676470588235294</v>
+        <v>0.0471976401179941</v>
       </c>
       <c r="Z4" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AA4" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3602941176470588</v>
+        <v>0.3657817109144543</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6954022988505747</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5084745762711864</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3775510204081632</v>
+        <v>0.3629032258064516</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.444444444444444</v>
+        <v>1.390804597701149</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.166666666666667</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.083333333333333</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6551724137931034</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.127659574468085</v>
+        <v>1.137931034482759</v>
       </c>
       <c r="AM4" t="n">
         <v>2</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.531914893617021</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.787234042553192</v>
+        <v>5.65</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.319148936170213</v>
+        <v>7.066666666666666</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.59999999999999</v>
+        <v>74.184</v>
       </c>
       <c r="C5" t="n">
-        <v>74.40000000000001</v>
+        <v>74.048</v>
       </c>
       <c r="D5" t="n">
-        <v>116.9354838709677</v>
+        <v>111.2791702679343</v>
       </c>
       <c r="E5" t="n">
-        <v>118.2795698924731</v>
+        <v>116.9511668107174</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5459558823529411</v>
+        <v>0.523598820058997</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1360741169658367</v>
+        <v>0.139886225869626</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3219178082191781</v>
+        <v>0.3068783068783069</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1875</v>
+        <v>0.168141592920354</v>
       </c>
       <c r="J5" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="K5" t="n">
-        <v>13.25</v>
+        <v>13.2</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>26</v>
+        <v>24.2</v>
       </c>
       <c r="O5" t="n">
-        <v>36</v>
+        <v>34.8</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5132743362831859</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="R5" t="n">
-        <v>14.75</v>
+        <v>13.6</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2169117647058824</v>
+        <v>0.2005899705014749</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04411764705882353</v>
+        <v>0.04129793510324484</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="X5" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03676470588235294</v>
+        <v>0.04719764011799411</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3602941176470588</v>
+        <v>0.3657817109144543</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6954022988505747</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5084745762711864</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3775510204081632</v>
+        <v>0.3629032258064516</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.444444444444444</v>
+        <v>1.390804597701149</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.166666666666667</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.083333333333333</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6551724137931034</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.127659574468085</v>
+        <v>1.137931034482759</v>
       </c>
       <c r="AM5" t="n">
         <v>2</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.531914893617021</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.787234042553192</v>
+        <v>5.649999999999999</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.319148936170213</v>
+        <v>7.066666666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1429,162 +1429,162 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
+        <v>16</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19</v>
+      </c>
+      <c r="K8" t="n">
+        <v>15</v>
+      </c>
+      <c r="L8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>8</v>
       </c>
-      <c r="J8" t="n">
-        <v>17</v>
-      </c>
-      <c r="K8" t="n">
-        <v>13</v>
-      </c>
-      <c r="L8" t="n">
-        <v>8</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>6</v>
-      </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
         <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T8" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="U8" t="n">
         <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Z8" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.706</v>
+        <v>0.786</v>
       </c>
       <c r="AB8" t="n">
         <v>4</v>
       </c>
       <c r="AC8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
         <v>5</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>4</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL8" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.238</v>
+        <v>0.259</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>240:53</t>
+          <t>288:23</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>51.52</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.452</v>
+        <v>0.455</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.483</v>
+        <v>0.516</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.854</v>
+        <v>0.914</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.143</v>
+        <v>0.255</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.833</v>
+        <v>2.375</v>
       </c>
       <c r="AV8" t="n">
-        <v>7</v>
+        <v>6.875</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.833</v>
+        <v>9.25</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.1</v>
+        <v>0.114</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.038</v>
+        <v>0.042</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.061</v>
+        <v>0.056</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.148</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="9">
@@ -1594,22 +1594,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D9" t="n">
+        <v>19</v>
+      </c>
+      <c r="E9" t="n">
+        <v>34</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
         <v>16</v>
-      </c>
-      <c r="E9" t="n">
-        <v>27</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -1618,40 +1618,40 @@
         <v>6</v>
       </c>
       <c r="J9" t="n">
+        <v>12</v>
+      </c>
+      <c r="K9" t="n">
+        <v>18</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" t="n">
         <v>7</v>
       </c>
-      <c r="K9" t="n">
-        <v>13</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>5</v>
-      </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>68</v>
+      </c>
+      <c r="U9" t="n">
         <v>7</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>7</v>
-      </c>
-      <c r="R9" t="n">
-        <v>9</v>
-      </c>
-      <c r="S9" t="n">
-        <v>8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>52</v>
-      </c>
-      <c r="U9" t="n">
-        <v>5</v>
       </c>
       <c r="V9" t="n">
         <v>8</v>
@@ -1663,22 +1663,22 @@
         <v>4</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z9" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.824</v>
+        <v>0.739</v>
       </c>
       <c r="AB9" t="n">
         <v>4</v>
       </c>
       <c r="AC9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.4</v>
+        <v>0.364</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -1693,63 +1693,63 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.308</v>
+        <v>0.357</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>170:26</t>
+          <t>236:57</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>49.64</v>
+        <v>61.64</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.541</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.967</v>
+        <v>0.925</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.141</v>
+        <v>0.146</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.714</v>
+        <v>5.556</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.714</v>
+        <v>6.889</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.137</v>
+        <v>0.122</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.053</v>
+        <v>0.046</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.063</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="10">
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.068</v>
+        <v>0.065</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -1924,43 +1924,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1972,19 +1972,19 @@
         <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="U11" t="n">
         <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W11" t="n">
         <v>4</v>
@@ -1993,13 +1993,13 @@
         <v>2</v>
       </c>
       <c r="Y11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="AB11" t="n">
         <v>1</v>
@@ -2023,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -2032,54 +2032,54 @@
         <v>3</v>
       </c>
       <c r="AL11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>118:53</t>
+          <t>147:11</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>26.64</v>
+        <v>34.52</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.477</v>
+        <v>0.431</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.528</v>
+        <v>0.492</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.976</v>
+        <v>0.927</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.075</v>
+        <v>0.058</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.227</v>
+        <v>0.241</v>
       </c>
       <c r="AU11" t="n">
         <v>1.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.105</v>
+        <v>0.11</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="12">
@@ -2089,22 +2089,22 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>23</v>
+      </c>
+      <c r="D12" t="n">
         <v>4</v>
       </c>
-      <c r="C12" t="n">
-        <v>18</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -2116,10 +2116,10 @@
         <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
         <v>3</v>
@@ -2131,22 +2131,22 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2158,13 +2158,13 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2185,66 +2185,66 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AK12" t="n">
         <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>104:00</t>
+          <t>146:27</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.575</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.575</v>
       </c>
       <c r="AR12" t="n">
-        <v>1</v>
+        <v>0.958</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.111</v>
+        <v>0.167</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AW12" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.081</v>
+        <v>0.077</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.043</v>
+        <v>0.037</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.12</v>
+        <v>0.089</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.048</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="13">
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>11</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
         <v>7</v>
       </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" t="n">
-        <v>5</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" t="n">
         <v>6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -2290,7 +2290,7 @@
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2302,34 +2302,34 @@
         <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
         <v>3</v>
       </c>
       <c r="W13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.9</v>
+        <v>0.917</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2350,66 +2350,66 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ13" t="n">
         <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.25</v>
+        <v>0.286</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>66:48</t>
+          <t>82:29</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>20.64</v>
+        <v>26.08</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.714</v>
+        <v>0.737</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.751</v>
+        <v>0.77</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.211</v>
+        <v>1.304</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.194</v>
+        <v>0.153</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.357</v>
+        <v>0.316</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.145</v>
+        <v>0.148</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.068</v>
+        <v>0.079</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.049</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="14">
@@ -2419,16 +2419,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -2437,16 +2437,16 @@
         <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J14" t="n">
         <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L14" t="n">
         <v>8</v>
@@ -2455,55 +2455,55 @@
         <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
+        <v>16</v>
+      </c>
+      <c r="S14" t="n">
+        <v>9</v>
+      </c>
+      <c r="T14" t="n">
+        <v>58</v>
+      </c>
+      <c r="U14" t="n">
+        <v>8</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6</v>
+      </c>
+      <c r="W14" t="n">
         <v>13</v>
       </c>
-      <c r="S14" t="n">
+      <c r="X14" t="n">
         <v>7</v>
       </c>
-      <c r="T14" t="n">
-        <v>42</v>
-      </c>
-      <c r="U14" t="n">
-        <v>6</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4</v>
-      </c>
-      <c r="W14" t="n">
-        <v>9</v>
-      </c>
-      <c r="X14" t="n">
-        <v>4</v>
-      </c>
       <c r="Y14" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Z14" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.839</v>
       </c>
       <c r="AB14" t="n">
         <v>3</v>
       </c>
       <c r="AC14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2534,47 +2534,47 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>136:57</t>
+          <t>155:54</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>38.64</v>
+        <v>47.4</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.516</v>
+        <v>0.539</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.601</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.009</v>
+        <v>1.076</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.188</v>
+        <v>0.263</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.132</v>
+        <v>0.142</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.066</v>
+        <v>0.056</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.058</v>
+        <v>0.09</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.052</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="15">
@@ -2584,43 +2584,43 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H15" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
         <v>7</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2632,43 +2632,43 @@
         <v>11</v>
       </c>
       <c r="R15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S15" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="T15" t="n">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="U15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="Z15" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.923</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.4</v>
+        <v>0.429</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2680,66 +2680,66 @@
         <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK15" t="n">
         <v>10</v>
       </c>
       <c r="AL15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.435</v>
+        <v>0.417</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>251:00</t>
+          <t>316:42</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>66.36</v>
+        <v>74.88</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.702</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.732</v>
+        <v>0.728</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.221</v>
+        <v>1.242</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.166</v>
+        <v>0.147</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.319</v>
+        <v>0.423</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.364</v>
+        <v>2.636</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.273</v>
+        <v>4.727</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.636</v>
+        <v>7.364</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.124</v>
+        <v>0.111</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.252</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="16">
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
@@ -2758,7 +2758,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2821,10 +2821,10 @@
         <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AB16" t="n">
         <v>1</v>
@@ -2864,38 +2864,38 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>33:48</t>
+          <t>45:51</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>5.88</v>
+        <v>6.88</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.515</v>
+        <v>0.41</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.68</v>
+        <v>0.581</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.34</v>
+        <v>0.291</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AU16" t="n">
         <v>2.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.082</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -2904,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.038</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="17">
@@ -2914,61 +2914,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>14</v>
+      </c>
+      <c r="J17" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="n">
+      <c r="K17" t="n">
         <v>13</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="L17" t="n">
         <v>10</v>
       </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>10</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8</v>
-      </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
         <v>10</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="U17" t="n">
         <v>2</v>
@@ -2983,19 +2983,19 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.545</v>
+        <v>0.583</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -3029,47 +3029,47 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>106:00</t>
+          <t>131:03</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>18.4</v>
+        <v>23.16</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.385</v>
+        <v>0.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.316</v>
+        <v>0.307</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.598</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.054</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.077</v>
+        <v>0.067</v>
       </c>
       <c r="AU17" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.081</v>
+        <v>0.083</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.107</v>
+        <v>0.108</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="18">
@@ -3079,22 +3079,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
       </c>
       <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
         <v>5</v>
       </c>
-      <c r="F18" t="n">
-        <v>4</v>
-      </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
         <v>3</v>
@@ -3103,7 +3103,7 @@
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -3112,7 +3112,7 @@
         <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
@@ -3127,7 +3127,7 @@
         <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -3139,7 +3139,7 @@
         <v>4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
@@ -3151,10 +3151,10 @@
         <v>5</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AB18" t="n">
         <v>3</v>
@@ -3184,57 +3184,57 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.444</v>
+        <v>0.385</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>150:54</t>
+          <t>183:24</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>20.32</v>
+        <v>25.32</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.733</v>
+        <v>0.625</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.766</v>
+        <v>0.657</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.23</v>
+        <v>1.106</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.197</v>
+        <v>0.158</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.063</v>
+        <v>0.065</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.033</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="19">
@@ -3244,40 +3244,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
         <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
         <v>5</v>
@@ -3292,13 +3292,13 @@
         <v>2</v>
       </c>
       <c r="R19" t="n">
+        <v>8</v>
+      </c>
+      <c r="S19" t="n">
         <v>6</v>
       </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
       <c r="T19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -3307,28 +3307,28 @@
         <v>4</v>
       </c>
       <c r="W19" t="n">
+        <v>5</v>
+      </c>
+      <c r="X19" t="n">
         <v>2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
       </c>
       <c r="Y19" t="n">
         <v>4</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.667</v>
+        <v>0.571</v>
       </c>
       <c r="AB19" t="n">
         <v>1</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3349,57 +3349,57 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.4</v>
+        <v>0.357</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>190:04</t>
+          <t>235:17</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>22.76</v>
+        <v>29.64</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.526</v>
+        <v>0.46</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.506</v>
+        <v>0.434</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.923</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.067</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.053</v>
+        <v>0.04</v>
       </c>
       <c r="AU19" t="n">
         <v>1.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.056</v>
+        <v>0.059</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.048</v>
+        <v>0.055</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.024</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="20">
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -3574,49 +3574,49 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>4</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3739,126 +3739,126 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>10</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AO22" t="n">
         <v>4</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>8</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO22" t="n">
-        <v>2</v>
       </c>
       <c r="AP22" t="n">
         <v>0</v>
@@ -3904,159 +3904,159 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>352</v>
+        <v>433</v>
       </c>
       <c r="D23" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E23" t="n">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="F23" t="n">
+        <v>51</v>
+      </c>
+      <c r="G23" t="n">
+        <v>160</v>
+      </c>
+      <c r="H23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I23" t="n">
+        <v>99</v>
+      </c>
+      <c r="J23" t="n">
+        <v>102</v>
+      </c>
+      <c r="K23" t="n">
+        <v>131</v>
+      </c>
+      <c r="L23" t="n">
+        <v>69</v>
+      </c>
+      <c r="M23" t="n">
+        <v>39</v>
+      </c>
+      <c r="N23" t="n">
+        <v>30</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>53</v>
+      </c>
+      <c r="R23" t="n">
+        <v>80</v>
+      </c>
+      <c r="S23" t="n">
+        <v>102</v>
+      </c>
+      <c r="T23" t="n">
+        <v>558</v>
+      </c>
+      <c r="U23" t="n">
+        <v>49</v>
+      </c>
+      <c r="V23" t="n">
+        <v>62</v>
+      </c>
+      <c r="W23" t="n">
+        <v>76</v>
+      </c>
+      <c r="X23" t="n">
         <v>42</v>
       </c>
-      <c r="G23" t="n">
-        <v>129</v>
-      </c>
-      <c r="H23" t="n">
-        <v>48</v>
-      </c>
-      <c r="I23" t="n">
-        <v>70</v>
-      </c>
-      <c r="J23" t="n">
-        <v>86</v>
-      </c>
-      <c r="K23" t="n">
-        <v>99</v>
-      </c>
-      <c r="L23" t="n">
-        <v>55</v>
-      </c>
-      <c r="M23" t="n">
-        <v>32</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="Y23" t="n">
+        <v>149</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>183</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="AB23" t="n">
         <v>20</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>45</v>
-      </c>
-      <c r="R23" t="n">
-        <v>64</v>
-      </c>
-      <c r="S23" t="n">
-        <v>80</v>
-      </c>
-      <c r="T23" t="n">
-        <v>448</v>
-      </c>
-      <c r="U23" t="n">
-        <v>40</v>
-      </c>
-      <c r="V23" t="n">
-        <v>48</v>
-      </c>
-      <c r="W23" t="n">
-        <v>60</v>
-      </c>
-      <c r="X23" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>113</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>137</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>19</v>
-      </c>
       <c r="AC23" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.413</v>
+        <v>0.37</v>
       </c>
       <c r="AE23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.556</v>
+        <v>0.6</v>
       </c>
       <c r="AH23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI23" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.25</v>
+        <v>0.286</v>
       </c>
       <c r="AK23" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AL23" t="n">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.339</v>
+        <v>0.326</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>825:00</t>
+          <t>1025:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>351.8</v>
+        <v>438.56</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.539</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.579</v>
+        <v>0.569</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.001</v>
+        <v>0.987</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.136</v>
+        <v>0.132</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.176</v>
+        <v>0.208</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.792</v>
+        <v>1.759</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.688</v>
+        <v>5.81</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.479</v>
+        <v>7.569</v>
       </c>
       <c r="AX23" t="n">
         <v>0.2</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.136</v>
+        <v>0.139</v>
       </c>
       <c r="BA23" t="n">
         <v>0</v>
@@ -4069,159 +4069,159 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>412</v>
+      </c>
+      <c r="D24" t="n">
+        <v>104</v>
+      </c>
+      <c r="E24" t="n">
+        <v>199</v>
+      </c>
+      <c r="F24" t="n">
+        <v>49</v>
+      </c>
+      <c r="G24" t="n">
+        <v>140</v>
+      </c>
+      <c r="H24" t="n">
+        <v>57</v>
+      </c>
+      <c r="I24" t="n">
+        <v>68</v>
+      </c>
+      <c r="J24" t="n">
+        <v>85</v>
+      </c>
+      <c r="K24" t="n">
+        <v>118</v>
+      </c>
+      <c r="L24" t="n">
+        <v>58</v>
+      </c>
+      <c r="M24" t="n">
+        <v>36</v>
+      </c>
+      <c r="N24" t="n">
+        <v>30</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>55</v>
+      </c>
+      <c r="R24" t="n">
+        <v>95</v>
+      </c>
+      <c r="S24" t="n">
+        <v>87</v>
+      </c>
+      <c r="T24" t="n">
+        <v>474</v>
+      </c>
+      <c r="U24" t="n">
+        <v>38</v>
+      </c>
+      <c r="V24" t="n">
+        <v>66</v>
+      </c>
+      <c r="W24" t="n">
+        <v>32</v>
+      </c>
+      <c r="X24" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>121</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>174</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>68</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AH24" t="n">
         <v>4</v>
       </c>
-      <c r="C24" t="n">
-        <v>348</v>
-      </c>
-      <c r="D24" t="n">
-        <v>90</v>
-      </c>
-      <c r="E24" t="n">
-        <v>164</v>
-      </c>
-      <c r="F24" t="n">
-        <v>39</v>
-      </c>
-      <c r="G24" t="n">
-        <v>108</v>
-      </c>
-      <c r="H24" t="n">
-        <v>51</v>
-      </c>
-      <c r="I24" t="n">
-        <v>60</v>
-      </c>
-      <c r="J24" t="n">
-        <v>72</v>
-      </c>
-      <c r="K24" t="n">
-        <v>91</v>
-      </c>
-      <c r="L24" t="n">
-        <v>47</v>
-      </c>
-      <c r="M24" t="n">
-        <v>32</v>
-      </c>
-      <c r="N24" t="n">
-        <v>20</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>44</v>
-      </c>
-      <c r="R24" t="n">
-        <v>75</v>
-      </c>
-      <c r="S24" t="n">
-        <v>68</v>
-      </c>
-      <c r="T24" t="n">
-        <v>404</v>
-      </c>
-      <c r="U24" t="n">
-        <v>34</v>
-      </c>
-      <c r="V24" t="n">
-        <v>53</v>
-      </c>
-      <c r="W24" t="n">
-        <v>28</v>
-      </c>
-      <c r="X24" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>104</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>144</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>59</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2</v>
-      </c>
       <c r="AI24" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AK24" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AL24" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.378</v>
+        <v>0.363</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>825:00</t>
+          <t>1025:00</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>345.4</v>
+        <v>428.92</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.546</v>
+        <v>0.524</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.583</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.008</v>
+        <v>0.961</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.136</v>
+        <v>0.14</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.188</v>
+        <v>0.168</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.532</v>
+        <v>1.417</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.787</v>
+        <v>5.65</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.319</v>
+        <v>7.067</v>
       </c>
       <c r="AX24" t="n">
         <v>0.2</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.064</v>
+        <v>0.061</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.125</v>
+        <v>0.126</v>
       </c>
       <c r="BA24" t="n">
         <v>0</v>
@@ -4293,162 +4293,162 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>12.8</v>
       </c>
       <c r="D26" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="E26" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G26" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="H26" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="I26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>83</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V26" t="n">
         <v>2</v>
       </c>
-      <c r="J26" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="W26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG26" t="n">
         <v>0.5</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T26" t="n">
-        <v>57</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
       <c r="AH26" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AI26" t="n">
         <v>1</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL26" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.238</v>
+        <v>0.259</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>60:13</t>
+          <t>57:40</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>12.88</v>
+        <v>14.008</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.452</v>
+        <v>0.455</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.483</v>
+        <v>0.516</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.854</v>
+        <v>0.914</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.143</v>
+        <v>0.255</v>
       </c>
       <c r="AU26" t="n">
-        <v>2.833</v>
+        <v>2.375</v>
       </c>
       <c r="AV26" t="n">
-        <v>7</v>
+        <v>6.875</v>
       </c>
       <c r="AW26" t="n">
-        <v>9.833</v>
+        <v>9.25</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.1</v>
+        <v>0.114</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.038</v>
+        <v>0.042</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.061</v>
+        <v>0.056</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.148</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="27">
@@ -4458,97 +4458,97 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="E27" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R27" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>68</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W27" t="n">
         <v>2</v>
       </c>
-      <c r="T27" t="n">
-        <v>52</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V27" t="n">
-        <v>2</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.5</v>
-      </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.824</v>
+        <v>0.739</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD27" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AE27" t="n">
         <v>0.4</v>
       </c>
-      <c r="AE27" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AF27" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AG27" t="n">
         <v>0.5</v>
@@ -4557,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
@@ -4566,54 +4566,54 @@
         <v>1</v>
       </c>
       <c r="AL27" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.308</v>
+        <v>0.357</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>42:36</t>
+          <t>47:23</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>12.41</v>
+        <v>12.328</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.541</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.967</v>
+        <v>0.925</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.141</v>
+        <v>0.146</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="AU27" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.714</v>
+        <v>5.556</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.714</v>
+        <v>6.889</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.137</v>
+        <v>0.122</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.053</v>
+        <v>0.046</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.063</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="28">
@@ -4775,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.068</v>
+        <v>0.065</v>
       </c>
       <c r="BA28" t="n">
         <v>0</v>
@@ -4788,162 +4788,162 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="D29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E29" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="F29" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="G29" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="K29" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="L29" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="M29" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="R29" t="n">
         <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="T29" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="U29" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="V29" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="X29" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AD29" t="n">
         <v>0.2</v>
       </c>
       <c r="AE29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM29" t="n">
         <v>0.25</v>
       </c>
-      <c r="AF29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>29:43</t>
+          <t>29:26</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>6.66</v>
+        <v>6.904</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.477</v>
+        <v>0.431</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.528</v>
+        <v>0.492</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.976</v>
+        <v>0.927</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.075</v>
+        <v>0.058</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.227</v>
+        <v>0.241</v>
       </c>
       <c r="AU29" t="n">
         <v>1.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.105</v>
+        <v>0.11</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="30">
@@ -4953,22 +4953,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="D30" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E30" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -4977,138 +4977,138 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T30" t="n">
+        <v>38</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>29:17</t>
+        </is>
+      </c>
+      <c r="AO30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
         <v>1.5</v>
       </c>
-      <c r="K30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>36</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>26:00</t>
-        </is>
-      </c>
-      <c r="AO30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3</v>
-      </c>
       <c r="AV30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AW30" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.081</v>
+        <v>0.077</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.043</v>
+        <v>0.037</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.12</v>
+        <v>0.089</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.048</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="31">
@@ -5118,88 +5118,88 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>6.25</v>
+        <v>6.8</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G31" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="H31" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L31" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="U31" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="V31" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="X31" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.9</v>
+        <v>0.917</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -5214,66 +5214,66 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AJ31" t="n">
         <v>1</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AL31" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.25</v>
+        <v>0.286</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>5.16</v>
+        <v>5.216</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.714</v>
+        <v>0.737</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.751</v>
+        <v>0.77</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.211</v>
+        <v>1.304</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.194</v>
+        <v>0.153</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.357</v>
+        <v>0.316</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AV31" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="AW31" t="n">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.145</v>
+        <v>0.148</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.068</v>
+        <v>0.079</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.049</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="32">
@@ -5283,43 +5283,43 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>9.75</v>
+        <v>10.2</v>
       </c>
       <c r="D32" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="E32" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="F32" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G32" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="H32" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K32" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -5331,43 +5331,43 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="S32" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="T32" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="U32" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="W32" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.839</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -5382,63 +5382,63 @@
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AJ32" t="n">
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AL32" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AM32" t="n">
         <v>0.125</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>34:14</t>
+          <t>31:10</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>9.66</v>
+        <v>9.48</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.516</v>
+        <v>0.539</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.601</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.009</v>
+        <v>1.076</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.188</v>
+        <v>0.263</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AW32" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.132</v>
+        <v>0.142</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.066</v>
+        <v>0.056</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.058</v>
+        <v>0.09</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.052</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="33">
@@ -5448,162 +5448,162 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T33" t="n">
+        <v>137</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
+      </c>
+      <c r="V33" t="n">
         <v>4</v>
       </c>
-      <c r="C33" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="D33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E33" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G33" t="n">
-        <v>6</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I33" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="J33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T33" t="n">
-        <v>112</v>
-      </c>
-      <c r="U33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4.25</v>
-      </c>
       <c r="W33" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="X33" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.25</v>
+        <v>7.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.75</v>
+        <v>7.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.923</v>
       </c>
       <c r="AB33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
       <c r="AK33" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AL33" t="n">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.435</v>
+        <v>0.417</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>62:45</t>
+          <t>63:20</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>16.59</v>
+        <v>14.976</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.702</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.732</v>
+        <v>0.728</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.221</v>
+        <v>1.242</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.166</v>
+        <v>0.147</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.319</v>
+        <v>0.423</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.364</v>
+        <v>2.636</v>
       </c>
       <c r="AV33" t="n">
-        <v>4.273</v>
+        <v>4.727</v>
       </c>
       <c r="AW33" t="n">
-        <v>6.636</v>
+        <v>7.364</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.124</v>
+        <v>0.111</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.252</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="34">
@@ -5613,88 +5613,88 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="E34" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AA34" t="n">
         <v>0.667</v>
       </c>
-      <c r="H34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1</v>
-      </c>
       <c r="AB34" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AD34" t="n">
         <v>1</v>
@@ -5712,7 +5712,7 @@
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
@@ -5721,45 +5721,45 @@
         <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AM34" t="n">
         <v>0</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.515</v>
+        <v>0.41</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.68</v>
+        <v>0.581</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.34</v>
+        <v>0.291</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AU34" t="n">
         <v>2.5</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AW34" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.082</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
@@ -5768,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.051</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="35">
@@ -5778,16 +5778,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="D35" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="E35" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -5796,144 +5796,144 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="L35" t="n">
         <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N35" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="R35" t="n">
+        <v>2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T35" t="n">
+        <v>19</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>26:12</t>
+        </is>
+      </c>
+      <c r="AO35" t="n">
+        <v>4.632</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AU35" t="n">
         <v>2.5</v>
       </c>
-      <c r="S35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T35" t="n">
-        <v>13</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>26:30</t>
-        </is>
-      </c>
-      <c r="AO35" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0.598</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3</v>
-      </c>
       <c r="AV35" t="n">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.081</v>
+        <v>0.083</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.107</v>
+        <v>0.108</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="36">
@@ -5943,88 +5943,88 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>6.25</v>
+        <v>5.6</v>
       </c>
       <c r="D36" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="H36" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="I36" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M36" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="N36" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="R36" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="S36" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="T36" t="n">
         <v>28</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W36" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="X36" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AD36" t="n">
         <v>1</v>
@@ -6042,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AJ36" t="n">
         <v>0</v>
@@ -6051,54 +6051,54 @@
         <v>1</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.444</v>
+        <v>0.385</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>37:43</t>
+          <t>36:40</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>5.08</v>
+        <v>5.064</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.733</v>
+        <v>0.625</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.766</v>
+        <v>0.657</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.23</v>
+        <v>1.106</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.197</v>
+        <v>0.158</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="AU36" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.063</v>
+        <v>0.065</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.033</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="37">
@@ -6108,97 +6108,97 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E37" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="H37" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="L37" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M37" t="n">
         <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>31</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD37" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T37" t="n">
-        <v>30</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1</v>
-      </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -6207,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AJ37" t="n">
         <v>0</v>
@@ -6216,54 +6216,54 @@
         <v>1</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.4</v>
+        <v>0.357</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>47:31</t>
+          <t>47:03</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>5.69</v>
+        <v>5.928</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.526</v>
+        <v>0.46</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.506</v>
+        <v>0.434</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.923</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.067</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.053</v>
+        <v>0.04</v>
       </c>
       <c r="AU37" t="n">
         <v>1.5</v>
       </c>
       <c r="AV37" t="n">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.056</v>
+        <v>0.059</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.048</v>
+        <v>0.055</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.024</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="38">
@@ -6273,7 +6273,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -6465,10 +6465,10 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="L39" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -6480,7 +6480,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -6657,7 +6657,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AP40" t="n">
         <v>0</v>
@@ -6768,159 +6768,159 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C41" t="n">
-        <v>88</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>22.25</v>
+        <v>21</v>
       </c>
       <c r="E41" t="n">
-        <v>36</v>
+        <v>35.4</v>
       </c>
       <c r="F41" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="G41" t="n">
-        <v>32.25</v>
+        <v>32</v>
       </c>
       <c r="H41" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I41" t="n">
-        <v>17.5</v>
+        <v>19.8</v>
       </c>
       <c r="J41" t="n">
-        <v>21.5</v>
+        <v>20.4</v>
       </c>
       <c r="K41" t="n">
-        <v>24.75</v>
+        <v>26.2</v>
       </c>
       <c r="L41" t="n">
-        <v>13.75</v>
+        <v>13.8</v>
       </c>
       <c r="M41" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="N41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>11.25</v>
+        <v>10.6</v>
       </c>
       <c r="R41" t="n">
         <v>16</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="T41" t="n">
-        <v>448</v>
+        <v>558</v>
       </c>
       <c r="U41" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V41" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="W41" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="X41" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Y41" t="n">
-        <v>28.25</v>
+        <v>29.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>34.25</v>
+        <v>36.6</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.825</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="AC41" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.413</v>
+        <v>0.37</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.556</v>
+        <v>0.6</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AI41" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.25</v>
+        <v>0.286</v>
       </c>
       <c r="AK41" t="n">
-        <v>9.25</v>
+        <v>8.6</v>
       </c>
       <c r="AL41" t="n">
-        <v>27.25</v>
+        <v>26.4</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.339</v>
+        <v>0.326</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>206:15</t>
+          <t>205:00</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>87.95</v>
+        <v>87.712</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.539</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.579</v>
+        <v>0.569</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.001</v>
+        <v>0.987</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.136</v>
+        <v>0.132</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.176</v>
+        <v>0.208</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.792</v>
+        <v>1.759</v>
       </c>
       <c r="AV41" t="n">
-        <v>5.688</v>
+        <v>5.81</v>
       </c>
       <c r="AW41" t="n">
-        <v>7.479</v>
+        <v>7.569</v>
       </c>
       <c r="AX41" t="n">
         <v>0.2</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.136</v>
+        <v>0.139</v>
       </c>
       <c r="BA41" t="n">
         <v>0</v>
@@ -6933,156 +6933,156 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C42" t="n">
-        <v>87</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>22.5</v>
+        <v>20.8</v>
       </c>
       <c r="E42" t="n">
-        <v>41</v>
+        <v>39.8</v>
       </c>
       <c r="F42" t="n">
-        <v>9.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H42" t="n">
-        <v>12.75</v>
+        <v>11.4</v>
       </c>
       <c r="I42" t="n">
-        <v>15</v>
+        <v>13.6</v>
       </c>
       <c r="J42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>22.75</v>
+        <v>23.6</v>
       </c>
       <c r="L42" t="n">
-        <v>11.75</v>
+        <v>11.6</v>
       </c>
       <c r="M42" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="N42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="Q42" t="n">
         <v>11</v>
       </c>
       <c r="R42" t="n">
-        <v>18.75</v>
+        <v>19</v>
       </c>
       <c r="S42" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="T42" t="n">
-        <v>404</v>
+        <v>474</v>
       </c>
       <c r="U42" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="V42" t="n">
-        <v>13.25</v>
+        <v>13.2</v>
       </c>
       <c r="W42" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="X42" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>26</v>
+        <v>24.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>36</v>
+        <v>34.8</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.722</v>
+        <v>0.695</v>
       </c>
       <c r="AB42" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>14.75</v>
+        <v>13.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.508</v>
+        <v>0.471</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AF42" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.583</v>
+        <v>0.571</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AK42" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="AL42" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.378</v>
+        <v>0.363</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>206:15</t>
+          <t>205:00</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>86.34999999999999</v>
+        <v>85.78400000000001</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.546</v>
+        <v>0.524</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.583</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.008</v>
+        <v>0.961</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.136</v>
+        <v>0.14</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.188</v>
+        <v>0.168</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.532</v>
+        <v>1.417</v>
       </c>
       <c r="AV42" t="n">
-        <v>5.787</v>
+        <v>5.65</v>
       </c>
       <c r="AW42" t="n">
-        <v>7.319</v>
+        <v>7.067</v>
       </c>
       <c r="AX42" t="n">
         <v>0.196</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.064</v>
+        <v>0.062</v>
       </c>
       <c r="AZ42" t="n">
         <v>0.125</v>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_VALENCIA BASKET.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_VALENCIA BASKET.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA42"/>
+  <dimension ref="A1:BA40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>369.56</v>
+        <v>446.52</v>
       </c>
       <c r="C2" t="n">
-        <v>370.24</v>
+        <v>447.72</v>
       </c>
       <c r="D2" t="n">
-        <v>116.9511668107174</v>
+        <v>116.8140802287144</v>
       </c>
       <c r="E2" t="n">
-        <v>111.2791702679343</v>
+        <v>115.4739569373716</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5385756676557863</v>
+        <v>0.5451219512195122</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1322510032834732</v>
+        <v>0.1277358346678868</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3689839572192513</v>
+        <v>0.3466666666666667</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2077151335311573</v>
+        <v>0.1853658536585366</v>
       </c>
       <c r="J2" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="N2" t="n">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="O2" t="n">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="P2" t="n">
-        <v>0.543026706231454</v>
+        <v>0.524390243902439</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R2" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1602373887240356</v>
+        <v>0.1682926829268293</v>
       </c>
       <c r="T2" t="n">
         <v>6</v>
       </c>
       <c r="U2" t="n">
+        <v>13</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.03170731707317073</v>
+      </c>
+      <c r="W2" t="n">
         <v>10</v>
       </c>
-      <c r="V2" t="n">
-        <v>0.02967359050445104</v>
-      </c>
-      <c r="W2" t="n">
-        <v>8</v>
-      </c>
       <c r="X2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0830860534124629</v>
+        <v>0.07804878048780488</v>
       </c>
       <c r="Z2" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AA2" t="n">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3916913946587537</v>
+        <v>0.3829268292682927</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8142076502732241</v>
+        <v>0.827906976744186</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.6</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3125</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3257575757575757</v>
+        <v>0.3248407643312102</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.628415300546448</v>
+        <v>1.655813953488372</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.2</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.95625</v>
+        <v>0.9682539682539683</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.07246376811594203</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8985507246376812</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.80952380952381</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.758620689655172</v>
+        <v>1.865671641791045</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.810344827586207</v>
+        <v>6.119402985074627</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.568965517241379</v>
+        <v>7.985074626865671</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.91200000000001</v>
+        <v>74.42</v>
       </c>
       <c r="C3" t="n">
-        <v>74.048</v>
+        <v>74.62</v>
       </c>
       <c r="D3" t="n">
-        <v>116.9511668107174</v>
+        <v>116.8140802287144</v>
       </c>
       <c r="E3" t="n">
-        <v>111.2791702679343</v>
+        <v>115.4739569373716</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5385756676557862</v>
+        <v>0.5451219512195121</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1322510032834732</v>
+        <v>0.1277358346678868</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3689839572192513</v>
+        <v>0.3466666666666667</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2077151335311573</v>
+        <v>0.1853658536585366</v>
       </c>
       <c r="J3" t="n">
-        <v>9.800000000000001</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K3" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>10.6</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="N3" t="n">
-        <v>29.8</v>
+        <v>29.66666666666667</v>
       </c>
       <c r="O3" t="n">
-        <v>36.6</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="P3" t="n">
-        <v>0.543026706231454</v>
+        <v>0.5243902439024389</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1602373887240356</v>
+        <v>0.1682926829268293</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02967359050445104</v>
+        <v>0.03170731707317073</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="X3" t="n">
-        <v>5.6</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08308605341246289</v>
+        <v>0.07804878048780486</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.4</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3916913946587536</v>
+        <v>0.3829268292682926</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8142076502732241</v>
+        <v>0.827906976744186</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.6</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2857142857142858</v>
+        <v>0.3125000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3257575757575757</v>
+        <v>0.3248407643312102</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.628415300546448</v>
+        <v>1.655813953488372</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.2</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9562499999999999</v>
+        <v>0.9682539682539683</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8166666666666668</v>
+        <v>0.07246376811594203</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8985507246376812</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.809523809523809</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.758620689655172</v>
+        <v>1.865671641791045</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.810344827586207</v>
+        <v>6.119402985074628</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.568965517241381</v>
+        <v>7.985074626865672</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>370.92</v>
+        <v>448.92</v>
       </c>
       <c r="C4" t="n">
-        <v>370.24</v>
+        <v>447.72</v>
       </c>
       <c r="D4" t="n">
-        <v>111.2791702679343</v>
+        <v>115.4739569373716</v>
       </c>
       <c r="E4" t="n">
-        <v>116.9511668107174</v>
+        <v>116.8140802287144</v>
       </c>
       <c r="F4" t="n">
-        <v>0.523598820058997</v>
+        <v>0.5276442307692307</v>
       </c>
       <c r="G4" t="n">
-        <v>0.139886225869626</v>
+        <v>0.1311986613933678</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3068783068783069</v>
+        <v>0.3347826086956522</v>
       </c>
       <c r="I4" t="n">
-        <v>0.168141592920354</v>
+        <v>0.1875</v>
       </c>
       <c r="J4" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N4" t="n">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="O4" t="n">
-        <v>174</v>
+        <v>225</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5132743362831859</v>
+        <v>0.5408653846153846</v>
       </c>
       <c r="Q4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R4" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2005899705014749</v>
+        <v>0.1899038461538461</v>
       </c>
       <c r="T4" t="n">
         <v>8</v>
       </c>
       <c r="U4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04129793510324484</v>
+        <v>0.03846153846153846</v>
       </c>
       <c r="W4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0471976401179941</v>
+        <v>0.05528846153846154</v>
       </c>
       <c r="Z4" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="AA4" t="n">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3657817109144543</v>
+        <v>0.3629807692307692</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6954022988505747</v>
+        <v>0.7155555555555555</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4303797468354431</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.25</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3629032258064516</v>
+        <v>0.3841059602649007</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.390804597701149</v>
+        <v>1.431111111111111</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.142857142857143</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.05</v>
+        <v>1.086206896551724</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6551724137931034</v>
+        <v>0.1343283582089552</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.137931034482759</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.416666666666667</v>
+        <v>1.565217391304348</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.65</v>
+        <v>6.028985507246377</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.066666666666666</v>
+        <v>7.594202898550725</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.184</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>74.048</v>
+        <v>74.62</v>
       </c>
       <c r="D5" t="n">
-        <v>111.2791702679343</v>
+        <v>115.4739569373716</v>
       </c>
       <c r="E5" t="n">
-        <v>116.9511668107174</v>
+        <v>116.8140802287144</v>
       </c>
       <c r="F5" t="n">
-        <v>0.523598820058997</v>
+        <v>0.5276442307692306</v>
       </c>
       <c r="G5" t="n">
-        <v>0.139886225869626</v>
+        <v>0.1311986613933678</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3068783068783069</v>
+        <v>0.3347826086956522</v>
       </c>
       <c r="I5" t="n">
-        <v>0.168141592920354</v>
+        <v>0.1875</v>
       </c>
       <c r="J5" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="N5" t="n">
-        <v>24.2</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="O5" t="n">
-        <v>34.8</v>
+        <v>37.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5132743362831859</v>
+        <v>0.5408653846153846</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.4</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="R5" t="n">
-        <v>13.6</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2005899705014749</v>
+        <v>0.1899038461538461</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="U5" t="n">
-        <v>2.8</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04129793510324484</v>
+        <v>0.03846153846153846</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="X5" t="n">
-        <v>3.2</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04719764011799411</v>
+        <v>0.05528846153846154</v>
       </c>
       <c r="Z5" t="n">
-        <v>9</v>
+        <v>9.666666666666666</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.8</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3657817109144543</v>
+        <v>0.3629807692307692</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6954022988505747</v>
+        <v>0.7155555555555555</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4705882352941177</v>
+        <v>0.4303797468354431</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.25</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3629032258064516</v>
+        <v>0.3841059602649006</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.390804597701149</v>
+        <v>1.431111111111111</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.142857142857143</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.05</v>
+        <v>1.086206896551724</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.6551724137931034</v>
+        <v>0.1343283582089552</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.137931034482759</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.416666666666667</v>
+        <v>1.565217391304348</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.649999999999999</v>
+        <v>6.028985507246378</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.066666666666666</v>
+        <v>7.594202898550726</v>
       </c>
     </row>
     <row r="7">
@@ -1429,22 +1429,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F8" t="n">
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H8" t="n">
         <v>14</v>
@@ -1453,16 +1453,16 @@
         <v>16</v>
       </c>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L8" t="n">
         <v>11</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1477,114 +1477,114 @@
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T8" t="n">
         <v>83</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Z8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.786</v>
+        <v>0.806</v>
       </c>
       <c r="AB8" t="n">
         <v>4</v>
       </c>
       <c r="AC8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.571</v>
+        <v>0.444</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AK8" t="n">
         <v>7</v>
       </c>
       <c r="AL8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.259</v>
+        <v>0.241</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>288:23</t>
+          <t>165:56</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>70.04000000000001</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.455</v>
+        <v>0.438</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.516</v>
+        <v>0.493</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.914</v>
+        <v>0.886</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.114</v>
+        <v>0.101</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.255</v>
+        <v>0.219</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.375</v>
+        <v>2.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.875</v>
+        <v>8</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.25</v>
+        <v>10.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.114</v>
+        <v>0.222</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.042</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.056</v>
+        <v>0.109</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.141</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="9">
@@ -1594,22 +1594,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -1618,13 +1618,13 @@
         <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M9" t="n">
         <v>7</v>
@@ -1636,49 +1636,49 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="U9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Z9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="AB9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.364</v>
+        <v>0.417</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -1699,57 +1699,57 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.357</v>
+        <v>0.333</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>236:57</t>
+          <t>162:00</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>61.64</v>
+        <v>75.64</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.53</v>
+        <v>0.542</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.541</v>
+        <v>0.552</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.925</v>
+        <v>0.899</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.146</v>
+        <v>0.185</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.08</v>
+        <v>0.068</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.333</v>
+        <v>1.143</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.556</v>
+        <v>4.214</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.889</v>
+        <v>5.357</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.122</v>
+        <v>0.218</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.046</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.082</v>
+        <v>0.138</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.091</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="10">
@@ -1819,13 +1819,13 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>2</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>83:27</t>
+          <t>33:27</t>
         </is>
       </c>
       <c r="AO10" t="n">
@@ -1905,13 +1905,13 @@
         <v>10</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.062</v>
+        <v>0.154</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.065</v>
+        <v>0.159</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -1924,28 +1924,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -1972,34 +1972,34 @@
         <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Z11" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.867</v>
+        <v>0.909</v>
       </c>
       <c r="AB11" t="n">
         <v>1</v>
@@ -2029,57 +2029,57 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.25</v>
+        <v>0.308</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>147:11</t>
+          <t>115:01</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>34.52</v>
+        <v>41.4</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.431</v>
+        <v>0.543</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.492</v>
+        <v>0.596</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.927</v>
+        <v>1.135</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.058</v>
+        <v>0.048</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.241</v>
+        <v>0.257</v>
       </c>
       <c r="AU11" t="n">
         <v>1.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.11</v>
+        <v>0.168</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.096</v>
+        <v>0.12</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="12">
@@ -2089,43 +2089,43 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>17</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M12" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>12</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L12" t="n">
-        <v>5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3</v>
-      </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2140,111 +2140,111 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>61</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
         <v>4</v>
       </c>
-      <c r="T12" t="n">
-        <v>38</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2</v>
-      </c>
       <c r="AI12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AK12" t="n">
         <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>146:27</t>
+          <t>79:44</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>24</v>
+        <v>35.88</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.575</v>
+        <v>0.597</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.575</v>
+        <v>0.596</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.958</v>
+        <v>1.059</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.167</v>
+        <v>0.111</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AV12" t="n">
-        <v>5</v>
+        <v>7.75</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.077</v>
+        <v>0.21</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.037</v>
+        <v>0.082</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.089</v>
+        <v>0.254</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.041</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="13">
@@ -2254,22 +2254,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H13" t="n">
         <v>6</v>
@@ -2278,49 +2278,49 @@
         <v>7</v>
       </c>
       <c r="J13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>11</v>
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -2359,54 +2359,54 @@
         <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>82:29</t>
+          <t>66:26</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>26.08</v>
+        <v>30.08</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.737</v>
+        <v>0.705</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.77</v>
+        <v>0.738</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.304</v>
+        <v>1.23</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.153</v>
+        <v>0.166</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.316</v>
+        <v>0.273</v>
       </c>
       <c r="AU13" t="n">
         <v>2</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.148</v>
+        <v>0.211</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.013</v>
+        <v>0.033</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.079</v>
+        <v>0.096</v>
       </c>
       <c r="BA13" t="n">
         <v>0.055</v>
@@ -2419,22 +2419,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H14" t="n">
         <v>10</v>
@@ -2443,19 +2443,19 @@
         <v>10</v>
       </c>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" t="n">
         <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2467,43 +2467,43 @@
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="U14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Z14" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.839</v>
+        <v>0.829</v>
       </c>
       <c r="AB14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.375</v>
+        <v>0.455</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2524,57 +2524,57 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>155:54</t>
+          <t>124:56</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>47.4</v>
+        <v>56.4</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.539</v>
+        <v>0.574</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.601</v>
+        <v>0.623</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.076</v>
+        <v>1.135</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.105</v>
+        <v>0.089</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.263</v>
+        <v>0.213</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.142</v>
+        <v>0.211</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.056</v>
+        <v>0.078</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.09</v>
+        <v>0.145</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.044</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="15">
@@ -2584,100 +2584,100 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L15" t="n">
         <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S15" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="T15" t="n">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="U15" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="V15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Z15" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.923</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AB15" t="n">
         <v>3</v>
       </c>
       <c r="AC15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.429</v>
+        <v>0.273</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AH15" t="n">
         <v>1</v>
@@ -2689,57 +2689,57 @@
         <v>0.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL15" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.417</v>
+        <v>0.375</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>316:42</t>
+          <t>171:52</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>74.88</v>
+        <v>94.2</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.728</v>
+        <v>0.665</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.242</v>
+        <v>1.146</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.147</v>
+        <v>0.138</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.423</v>
+        <v>0.368</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.636</v>
+        <v>2.923</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.727</v>
+        <v>5.231</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.364</v>
+        <v>8.154</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.111</v>
+        <v>0.256</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.017</v>
+        <v>0.032</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.055</v>
+        <v>0.112</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.23</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="16">
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
@@ -2758,7 +2758,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2773,13 +2773,13 @@
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -2797,13 +2797,13 @@
         <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2812,19 +2812,19 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AB16" t="n">
         <v>1</v>
@@ -2864,47 +2864,47 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>45:51</t>
+          <t>29:21</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>6.88</v>
+        <v>7.88</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.581</v>
+        <v>0.508</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.291</v>
+        <v>0.254</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AU16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV16" t="n">
         <v>2.5</v>
       </c>
-      <c r="AV16" t="n">
-        <v>2</v>
-      </c>
       <c r="AW16" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.125</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.032</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="17">
@@ -2914,16 +2914,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2935,16 +2935,16 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
@@ -2956,40 +2956,40 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
         <v>2</v>
       </c>
       <c r="R17" t="n">
+        <v>12</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
+        <v>26</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>10</v>
       </c>
-      <c r="S17" t="n">
-        <v>9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>19</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>7</v>
-      </c>
       <c r="Z17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.583</v>
+        <v>0.667</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -3029,47 +3029,47 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>131:03</t>
+          <t>86:50</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>23.16</v>
+        <v>28.04</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.307</v>
+        <v>0.379</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.678</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.067</v>
+        <v>0.056</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.5</v>
+        <v>1.667</v>
       </c>
       <c r="AV17" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AW17" t="n">
-        <v>10</v>
+        <v>7.667</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.083</v>
+        <v>0.151</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.108</v>
+        <v>0.184</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.033</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="18">
@@ -3079,22 +3079,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
       </c>
       <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" t="n">
         <v>6</v>
       </c>
-      <c r="F18" t="n">
-        <v>5</v>
-      </c>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H18" t="n">
         <v>3</v>
@@ -3103,10 +3103,10 @@
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -3127,25 +3127,25 @@
         <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>5</v>
@@ -3160,10 +3160,10 @@
         <v>3</v>
       </c>
       <c r="AC18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3184,57 +3184,57 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.385</v>
+        <v>0.375</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>183:24</t>
+          <t>96:58</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>25.32</v>
+        <v>29.32</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.625</v>
+        <v>0.583</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.657</v>
+        <v>0.612</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.106</v>
+        <v>1.057</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.158</v>
+        <v>0.136</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.15</v>
+        <v>0.125</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AV18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.5</v>
+        <v>7.75</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.065</v>
+        <v>0.141</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.012</v>
+        <v>0.033</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.041</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="19">
@@ -3244,22 +3244,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -3271,7 +3271,7 @@
         <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L19" t="n">
         <v>7</v>
@@ -3298,19 +3298,19 @@
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>4</v>
@@ -3325,10 +3325,10 @@
         <v>1</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3349,57 +3349,57 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.357</v>
+        <v>0.4</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>235:17</t>
+          <t>92:29</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>29.64</v>
+        <v>31.64</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.46</v>
+        <v>0.481</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.434</v>
+        <v>0.455</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.853</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.067</v>
+        <v>0.063</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="AU19" t="n">
         <v>1.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.059</v>
+        <v>0.16</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.033</v>
+        <v>0.082</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.055</v>
+        <v>0.15</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="20">
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -3735,163 +3735,163 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" t="n">
+        <v>523</v>
+      </c>
+      <c r="D22" t="n">
+        <v>132</v>
+      </c>
+      <c r="E22" t="n">
+        <v>221</v>
+      </c>
+      <c r="F22" t="n">
+        <v>61</v>
+      </c>
+      <c r="G22" t="n">
+        <v>189</v>
+      </c>
+      <c r="H22" t="n">
+        <v>76</v>
+      </c>
+      <c r="I22" t="n">
+        <v>108</v>
+      </c>
+      <c r="J22" t="n">
+        <v>125</v>
+      </c>
+      <c r="K22" t="n">
+        <v>153</v>
+      </c>
+      <c r="L22" t="n">
+        <v>78</v>
+      </c>
+      <c r="M22" t="n">
+        <v>44</v>
+      </c>
+      <c r="N22" t="n">
+        <v>37</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>61</v>
+      </c>
+      <c r="R22" t="n">
+        <v>100</v>
+      </c>
+      <c r="S22" t="n">
+        <v>120</v>
+      </c>
+      <c r="T22" t="n">
+        <v>664</v>
+      </c>
+      <c r="U22" t="n">
         <v>5</v>
       </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>178</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>215</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>69</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="AH22" t="n">
         <v>10</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>0.325</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>1225:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>4</v>
+        <v>524.52</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>0.572</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>0.997</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.866</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>6.119</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>7.985</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -3900,163 +3900,163 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>433</v>
+        <v>517</v>
       </c>
       <c r="D23" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="E23" t="n">
-        <v>177</v>
+        <v>242</v>
       </c>
       <c r="F23" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G23" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="H23" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I23" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="J23" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="K23" t="n">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="L23" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="M23" t="n">
         <v>39</v>
       </c>
       <c r="N23" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>63</v>
+      </c>
+      <c r="R23" t="n">
+        <v>113</v>
+      </c>
+      <c r="S23" t="n">
+        <v>108</v>
+      </c>
+      <c r="T23" t="n">
+        <v>608</v>
+      </c>
+      <c r="U23" t="n">
+        <v>9</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>161</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>225</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>79</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="AK23" t="n">
         <v>58</v>
       </c>
-      <c r="Q23" t="n">
-        <v>53</v>
-      </c>
-      <c r="R23" t="n">
-        <v>80</v>
-      </c>
-      <c r="S23" t="n">
-        <v>102</v>
-      </c>
-      <c r="T23" t="n">
-        <v>558</v>
-      </c>
-      <c r="U23" t="n">
-        <v>49</v>
-      </c>
-      <c r="V23" t="n">
-        <v>62</v>
-      </c>
-      <c r="W23" t="n">
-        <v>76</v>
-      </c>
-      <c r="X23" t="n">
-        <v>42</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>149</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>183</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>54</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>43</v>
-      </c>
       <c r="AL23" t="n">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.326</v>
+        <v>0.384</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>1025:00</t>
+          <t>1225:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>438.56</v>
+        <v>525.92</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.539</v>
+        <v>0.528</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.569</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.987</v>
+        <v>0.983</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.132</v>
+        <v>0.131</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.208</v>
+        <v>0.188</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.759</v>
+        <v>1.565</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.81</v>
+        <v>6.029</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.569</v>
+        <v>7.594</v>
       </c>
       <c r="AX23" t="n">
         <v>0.2</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.074</v>
+        <v>0.067</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.139</v>
+        <v>0.131</v>
       </c>
       <c r="BA23" t="n">
         <v>0</v>
@@ -4065,601 +4065,601 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>5</v>
-      </c>
-      <c r="C24" t="n">
-        <v>412</v>
-      </c>
-      <c r="D24" t="n">
-        <v>104</v>
-      </c>
-      <c r="E24" t="n">
-        <v>199</v>
-      </c>
-      <c r="F24" t="n">
-        <v>49</v>
-      </c>
-      <c r="G24" t="n">
-        <v>140</v>
-      </c>
-      <c r="H24" t="n">
-        <v>57</v>
-      </c>
-      <c r="I24" t="n">
-        <v>68</v>
-      </c>
-      <c r="J24" t="n">
-        <v>85</v>
-      </c>
-      <c r="K24" t="n">
-        <v>118</v>
-      </c>
-      <c r="L24" t="n">
-        <v>58</v>
-      </c>
-      <c r="M24" t="n">
-        <v>36</v>
-      </c>
-      <c r="N24" t="n">
-        <v>30</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>55</v>
-      </c>
-      <c r="R24" t="n">
-        <v>95</v>
-      </c>
-      <c r="S24" t="n">
-        <v>87</v>
-      </c>
-      <c r="T24" t="n">
-        <v>474</v>
-      </c>
-      <c r="U24" t="n">
-        <v>38</v>
-      </c>
-      <c r="V24" t="n">
-        <v>66</v>
-      </c>
-      <c r="W24" t="n">
-        <v>32</v>
-      </c>
-      <c r="X24" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>121</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>174</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>68</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>45</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>124</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0.363</v>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>1025:00</t>
-        </is>
-      </c>
-      <c r="AO24" t="n">
-        <v>428.92</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0.961</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.417</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>7.067</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr"/>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
-      <c r="AY25" t="inlineStr"/>
-      <c r="AZ25" t="inlineStr"/>
-      <c r="BA25" t="inlineStr"/>
+          <t>#0 B. BADIO (Per Game)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>11.667</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.833</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>83</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.167</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>27:39</t>
+        </is>
+      </c>
+      <c r="AO25" t="n">
+        <v>13.173</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0.118</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>#0 B. BADIO (Per Game)</t>
+          <t>#1 K. TAYLOR (Per Game)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>12.8</v>
+        <v>11.333</v>
       </c>
       <c r="D26" t="n">
-        <v>2.6</v>
+        <v>3.833</v>
       </c>
       <c r="E26" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>6.4</v>
+        <v>3.333</v>
       </c>
       <c r="H26" t="n">
-        <v>2.8</v>
+        <v>0.667</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>3.8</v>
+        <v>2.667</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="L26" t="n">
-        <v>2.2</v>
+        <v>2.167</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6</v>
+        <v>1.167</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6</v>
+        <v>0.333</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.6</v>
+        <v>2.333</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.4</v>
+        <v>2.333</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>2.167</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>2.167</v>
       </c>
       <c r="T26" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2</v>
       </c>
-      <c r="W26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AD26" t="n">
-        <v>0.571</v>
+        <v>0.417</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="AG26" t="n">
         <v>0.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
         <v>1</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AL26" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.259</v>
+        <v>0.333</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>57:40</t>
+          <t>27:00</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>14.008</v>
+        <v>12.607</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.455</v>
+        <v>0.542</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.516</v>
+        <v>0.552</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.914</v>
+        <v>0.899</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.114</v>
+        <v>0.185</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.255</v>
+        <v>0.068</v>
       </c>
       <c r="AU26" t="n">
-        <v>2.375</v>
+        <v>1.143</v>
       </c>
       <c r="AV26" t="n">
-        <v>6.875</v>
+        <v>4.214</v>
       </c>
       <c r="AW26" t="n">
-        <v>9.25</v>
+        <v>5.357</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.114</v>
+        <v>0.218</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.042</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.056</v>
+        <v>0.138</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.141</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#1 K. TAYLOR (Per Game)</t>
+          <t>#2 J. PUERTO (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>11.4</v>
+        <v>3.333</v>
       </c>
       <c r="D27" t="n">
-        <v>3.8</v>
+        <v>0.667</v>
       </c>
       <c r="E27" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="T27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AA27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N27" t="n">
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AM27" t="n">
         <v>0.4</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T27" t="n">
-        <v>68</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AG27" t="n">
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AO27" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="AP27" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>47:23</t>
-        </is>
-      </c>
-      <c r="AO27" t="n">
-        <v>12.328</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0.53</v>
-      </c>
       <c r="AQ27" t="n">
-        <v>0.541</v>
+        <v>0.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.925</v>
+        <v>0.909</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.146</v>
+        <v>0.091</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.556</v>
+        <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.889</v>
+        <v>10</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.122</v>
+        <v>0.154</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.046</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.082</v>
+        <v>0.159</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#2 J. PUERTO (Per Game)</t>
+          <t>#3 N. REUVERS (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>3.333</v>
+        <v>7.833</v>
       </c>
       <c r="D28" t="n">
-        <v>0.667</v>
+        <v>2.167</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>3.167</v>
       </c>
       <c r="F28" t="n">
         <v>0.667</v>
       </c>
       <c r="G28" t="n">
-        <v>2.333</v>
+        <v>2.667</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>1.667</v>
+        <v>2.167</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4671,58 +4671,58 @@
         <v>0.333</v>
       </c>
       <c r="R28" t="n">
-        <v>0.667</v>
+        <v>2</v>
       </c>
       <c r="S28" t="n">
-        <v>0.667</v>
+        <v>1.833</v>
       </c>
       <c r="T28" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.667</v>
+        <v>3.333</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.667</v>
+        <v>3.667</v>
       </c>
       <c r="AA28" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1</v>
       </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
       <c r="AH28" t="n">
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
@@ -4731,925 +4731,925 @@
         <v>0.667</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.667</v>
+        <v>2.167</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.4</v>
+        <v>0.308</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>27:49</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>3.667</v>
+        <v>6.9</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.5</v>
+        <v>0.543</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.5</v>
+        <v>0.596</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.909</v>
+        <v>1.135</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.091</v>
+        <v>0.048</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>0.257</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.062</v>
+        <v>0.168</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.065</v>
+        <v>0.12</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#3 N. REUVERS (Per Game)</t>
+          <t>#4 J. PRADILLA (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>6.4</v>
+        <v>6.333</v>
       </c>
       <c r="D29" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="E29" t="n">
-        <v>2.8</v>
+        <v>2.333</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6</v>
+        <v>1.167</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2.833</v>
       </c>
       <c r="H29" t="n">
-        <v>1.4</v>
+        <v>0.167</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>0.333</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6</v>
+        <v>1.167</v>
       </c>
       <c r="K29" t="n">
-        <v>2.6</v>
+        <v>3.167</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8</v>
+        <v>0.333</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>0.167</v>
       </c>
       <c r="S29" t="n">
-        <v>1.8</v>
+        <v>1.167</v>
       </c>
       <c r="T29" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="U29" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.6</v>
+        <v>1.333</v>
       </c>
       <c r="Z29" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.867</v>
+        <v>0.889</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AC29" t="n">
         <v>1</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.6</v>
+        <v>1.333</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>29:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>6.904</v>
+        <v>5.98</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.431</v>
+        <v>0.597</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.492</v>
+        <v>0.596</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.927</v>
+        <v>1.059</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.058</v>
+        <v>0.111</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.241</v>
+        <v>0.032</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AV29" t="n">
-        <v>14.5</v>
+        <v>7.75</v>
       </c>
       <c r="AW29" t="n">
-        <v>16</v>
+        <v>9.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.015</v>
+        <v>0.082</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.096</v>
+        <v>0.254</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.021</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#4 J. PRADILLA (Per Game)</t>
+          <t>#5 S. DE LARREA (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>4.6</v>
+        <v>6.167</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="E30" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F30" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="H30" t="n">
         <v>1</v>
       </c>
-      <c r="G30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="J30" t="n">
-        <v>1.2</v>
+        <v>1.667</v>
       </c>
       <c r="K30" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="T30" t="n">
+        <v>42</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>1</v>
       </c>
-      <c r="M30" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>38</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AK30" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>29:17</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>4.8</v>
+        <v>5.013</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.575</v>
+        <v>0.705</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.575</v>
+        <v>0.738</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.958</v>
+        <v>1.23</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.167</v>
+        <v>0.166</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.077</v>
+        <v>0.211</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.089</v>
+        <v>0.096</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.041</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#5 S. DE LARREA (Per Game)</t>
+          <t>#7 B. KEY (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>6.8</v>
+        <v>10.667</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>1.2</v>
+        <v>0.333</v>
       </c>
       <c r="G31" t="n">
-        <v>2.2</v>
+        <v>1.833</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2</v>
+        <v>1.667</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>1.667</v>
       </c>
       <c r="J31" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K31" t="n">
-        <v>1.2</v>
+        <v>2.833</v>
       </c>
       <c r="L31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>77</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5.833</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AM31" t="n">
         <v>0.2</v>
       </c>
-      <c r="M31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>40</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0.286</v>
-      </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>5.216</v>
+        <v>9.4</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.737</v>
+        <v>0.574</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.77</v>
+        <v>0.623</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.304</v>
+        <v>1.135</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.153</v>
+        <v>0.089</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.316</v>
+        <v>0.213</v>
       </c>
       <c r="AU31" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.75</v>
+        <v>9.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.75</v>
+        <v>11.2</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.148</v>
+        <v>0.211</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.013</v>
+        <v>0.078</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.079</v>
+        <v>0.145</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#7 B. KEY (Per Game)</t>
+          <t>#8 J. MONTERO (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>18</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="I32" t="n">
         <v>5</v>
       </c>
-      <c r="C32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="D32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="T32" t="n">
+        <v>158</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK32" t="n">
         <v>2</v>
       </c>
-      <c r="I32" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T32" t="n">
-        <v>58</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.839</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD32" t="n">
+      <c r="AL32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="AM32" t="n">
         <v>0.375</v>
       </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0.125</v>
-      </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>31:10</t>
+          <t>28:38</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>9.48</v>
+        <v>15.7</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.539</v>
+        <v>0.61</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.601</v>
+        <v>0.665</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.076</v>
+        <v>1.146</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.105</v>
+        <v>0.138</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.263</v>
+        <v>0.368</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.2</v>
+        <v>2.923</v>
       </c>
       <c r="AV32" t="n">
-        <v>7.6</v>
+        <v>5.231</v>
       </c>
       <c r="AW32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.154</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.142</v>
+        <v>0.256</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.056</v>
+        <v>0.032</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.09</v>
+        <v>0.112</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.044</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#8 J. MONTERO (Per Game)</t>
+          <t>#10 O. MOORE (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>18.6</v>
+        <v>0.8</v>
       </c>
       <c r="D33" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="E33" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="F33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="H33" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="I33" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="J33" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="K33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1</v>
       </c>
-      <c r="M33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S33" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T33" t="n">
-        <v>137</v>
-      </c>
-      <c r="U33" t="n">
-        <v>3</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4</v>
-      </c>
-      <c r="W33" t="n">
-        <v>4</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.429</v>
-      </c>
       <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="AO33" t="n">
+        <v>1.576</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="AT33" t="n">
         <v>0.4</v>
       </c>
-      <c r="AF33" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>63:20</t>
-        </is>
-      </c>
-      <c r="AO33" t="n">
-        <v>14.976</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0.728</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.242</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0.423</v>
-      </c>
       <c r="AU33" t="n">
-        <v>2.636</v>
+        <v>3.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>4.727</v>
+        <v>2.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>7.364</v>
+        <v>6</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.111</v>
+        <v>0.125</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.017</v>
+        <v>0.037</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.23</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#10 O. MOORE (Per Game)</t>
+          <t>#12 N. SAKO (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>3.167</v>
       </c>
       <c r="D34" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5</v>
+        <v>0.167</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>2.667</v>
       </c>
       <c r="J34" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5658,16 +5658,16 @@
         <v>0.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="R34" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
-        <v>0.25</v>
+        <v>1.833</v>
       </c>
       <c r="T34" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -5676,28 +5676,28 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.5</v>
+        <v>1.667</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="AA34" t="n">
         <v>0.667</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.25</v>
+        <v>0.667</v>
       </c>
       <c r="AD34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -5712,7 +5712,7 @@
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
@@ -5721,124 +5721,124 @@
         <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
         <v>0</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>1.72</v>
+        <v>4.673</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.41</v>
+        <v>0.379</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.581</v>
+        <v>0.678</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.291</v>
+        <v>0.107</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.5</v>
+        <v>0.056</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.5</v>
+        <v>1.667</v>
       </c>
       <c r="AV34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.5</v>
+        <v>7.667</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.151</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>0.184</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.04</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#12 N. SAKO (Per Game)</t>
+          <t>#13 D. THOMPSON (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>2.6</v>
+        <v>5.167</v>
       </c>
       <c r="D35" t="n">
-        <v>1.2</v>
+        <v>0.833</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>1.167</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2.833</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2</v>
-      </c>
       <c r="S35" t="n">
-        <v>1.8</v>
+        <v>0.833</v>
       </c>
       <c r="T35" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="U35" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -5847,193 +5847,193 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.4</v>
+        <v>0.833</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AO35" t="n">
+        <v>4.887</v>
+      </c>
+      <c r="AP35" t="n">
         <v>0.583</v>
       </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>26:12</t>
-        </is>
-      </c>
-      <c r="AO35" t="n">
-        <v>4.632</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AQ35" t="n">
-        <v>0.307</v>
+        <v>0.612</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.5610000000000001</v>
+        <v>1.057</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.136</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.067</v>
+        <v>0.125</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AV35" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AW35" t="n">
-        <v>10</v>
+        <v>7.75</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.083</v>
+        <v>0.141</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.022</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.108</v>
+        <v>0.033</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.033</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#13 D. THOMPSON (Per Game)</t>
+          <t>#24 M. COSTELLO (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="E36" t="n">
-        <v>1.2</v>
+        <v>1.667</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>2.8</v>
+        <v>2.833</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6</v>
+        <v>0.167</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4</v>
+        <v>2.167</v>
       </c>
       <c r="L36" t="n">
-        <v>0.4</v>
+        <v>1.167</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="N36" t="n">
-        <v>0.2</v>
+        <v>0.833</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.8</v>
+        <v>0.333</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.8</v>
+        <v>0.333</v>
       </c>
       <c r="R36" t="n">
-        <v>0.8</v>
+        <v>1.333</v>
       </c>
       <c r="S36" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="U36" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.833</v>
+        <v>0.571</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.6</v>
+        <v>0.167</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -6042,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AJ36" t="n">
         <v>0</v>
@@ -6051,154 +6051,154 @@
         <v>1</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.385</v>
+        <v>0.4</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>36:40</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>5.064</v>
+        <v>5.273</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.625</v>
+        <v>0.481</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.657</v>
+        <v>0.455</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.106</v>
+        <v>0.853</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.158</v>
+        <v>0.063</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.15</v>
+        <v>0.037</v>
       </c>
       <c r="AU36" t="n">
         <v>1.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>5</v>
+        <v>13.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>6.5</v>
+        <v>15</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.065</v>
+        <v>0.16</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.012</v>
+        <v>0.082</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.012</v>
+        <v>0.15</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.041</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#24 M. COSTELLO (Per Game)</t>
+          <t>#32 I. NOGUES (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -6207,73 +6207,73 @@
         <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>47:03</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>5.928</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.434</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#32 I. NOGUES (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -6300,10 +6300,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -6315,7 +6315,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6434,68 +6434,68 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>87.167</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>36.833</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>10.167</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>12.667</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>20.833</v>
       </c>
       <c r="K39" t="n">
-        <v>1.2</v>
+        <v>25.5</v>
       </c>
       <c r="L39" t="n">
-        <v>1.6</v>
+        <v>13</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>7.333</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>6.167</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.8</v>
+        <v>11.167</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>10.167</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>16.667</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>664</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -6507,90 +6507,90 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>29.667</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>35.833</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>0.828</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>0.348</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.167</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>5.333</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>26.167</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>0.325</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>204:10</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>87.42</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>0.572</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>0.997</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>1.866</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>6.119</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>7.985</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="BA39" t="n">
         <v>0</v>
@@ -6599,68 +6599,68 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>86.167</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>20.833</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>40.333</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>12.833</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>6.167</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>18.833</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T40" t="n">
-        <v>10</v>
+        <v>608</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6672,422 +6672,92 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>26.833</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>0.716</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>5.667</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>13.167</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>3.833</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>0.217</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>9.667</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>25.167</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>0.384</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>204:10</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>0.8</v>
+        <v>87.65300000000001</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>0.528</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>0.983</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>0.131</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>0.187</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>1.565</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>6.029</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>7.594</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>0.201</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>5</v>
-      </c>
-      <c r="C41" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="D41" t="n">
-        <v>21</v>
-      </c>
-      <c r="E41" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="F41" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="G41" t="n">
-        <v>32</v>
-      </c>
-      <c r="H41" t="n">
-        <v>14</v>
-      </c>
-      <c r="I41" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="J41" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="K41" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="L41" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="M41" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="N41" t="n">
-        <v>6</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="R41" t="n">
-        <v>16</v>
-      </c>
-      <c r="S41" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="T41" t="n">
-        <v>558</v>
-      </c>
-      <c r="U41" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V41" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="W41" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X41" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>205:00</t>
-        </is>
-      </c>
-      <c r="AO41" t="n">
-        <v>87.712</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>1.759</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>7.569</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>5</v>
-      </c>
-      <c r="C42" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="D42" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="E42" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="F42" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G42" t="n">
-        <v>28</v>
-      </c>
-      <c r="H42" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="I42" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J42" t="n">
-        <v>17</v>
-      </c>
-      <c r="K42" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="L42" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M42" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N42" t="n">
-        <v>6</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>11</v>
-      </c>
-      <c r="R42" t="n">
-        <v>19</v>
-      </c>
-      <c r="S42" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="T42" t="n">
-        <v>474</v>
-      </c>
-      <c r="U42" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="V42" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="W42" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="X42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>9</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0.363</v>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>205:00</t>
-        </is>
-      </c>
-      <c r="AO42" t="n">
-        <v>85.78400000000001</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0.961</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>1.417</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>7.067</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="BA42" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_VALENCIA BASKET.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_VALENCIA BASKET.xlsx
@@ -671,13 +671,13 @@
         <v>0.1853658536585366</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M2" t="n">
         <v>61</v>
@@ -752,13 +752,13 @@
         <v>0.9682539682539683</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.07246376811594203</v>
+        <v>0.855072463768116</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>0.9102564102564102</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.703703703703704</v>
       </c>
       <c r="AN2" t="n">
         <v>1.865671641791045</v>
@@ -801,13 +801,13 @@
         <v>0.1853658536585366</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8333333333333334</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="M3" t="n">
         <v>10.16666666666667</v>
@@ -882,13 +882,13 @@
         <v>0.9682539682539683</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.07246376811594203</v>
+        <v>0.855072463768116</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.9102564102564104</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.703703703703704</v>
       </c>
       <c r="AN3" t="n">
         <v>1.865671641791045</v>
@@ -931,13 +931,13 @@
         <v>0.1875</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M4" t="n">
         <v>63</v>
@@ -1012,13 +1012,13 @@
         <v>1.086206896551724</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.1343283582089552</v>
+        <v>0.6119402985074627</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.807692307692308</v>
       </c>
       <c r="AN4" t="n">
         <v>1.565217391304348</v>
@@ -1061,13 +1061,13 @@
         <v>0.1875</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="M5" t="n">
         <v>10.5</v>
@@ -1142,13 +1142,13 @@
         <v>1.086206896551724</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1343283582089552</v>
+        <v>0.6119402985074627</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.807692307692308</v>
       </c>
       <c r="AN5" t="n">
         <v>1.565217391304348</v>
@@ -1486,16 +1486,16 @@
         <v>83</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="n">
         <v>25</v>
@@ -1651,16 +1651,16 @@
         <v>81</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="n">
         <v>20</v>
@@ -1819,13 +1819,13 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
         <v>2</v>
@@ -1981,16 +1981,16 @@
         <v>49</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="n">
         <v>20</v>
@@ -2146,16 +2146,16 @@
         <v>61</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
         <v>8</v>
@@ -2311,16 +2311,16 @@
         <v>42</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="n">
         <v>11</v>
@@ -2476,16 +2476,16 @@
         <v>77</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y14" t="n">
         <v>29</v>
@@ -2641,16 +2641,16 @@
         <v>158</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="n">
         <v>42</v>
@@ -2812,10 +2812,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
         <v>2</v>
@@ -2971,10 +2971,10 @@
         <v>26</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3136,16 +3136,16 @@
         <v>30</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="n">
         <v>5</v>
@@ -3304,13 +3304,13 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
         <v>4</v>
@@ -3796,16 +3796,16 @@
         <v>664</v>
       </c>
       <c r="U22" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="Y22" t="n">
         <v>178</v>
@@ -3961,16 +3961,16 @@
         <v>608</v>
       </c>
       <c r="U23" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y23" t="n">
         <v>161</v>
@@ -4185,16 +4185,16 @@
         <v>83</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="Y25" t="n">
         <v>4.167</v>
@@ -4350,16 +4350,16 @@
         <v>81</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
         <v>3.333</v>
@@ -4518,13 +4518,13 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y27" t="n">
         <v>0.667</v>
@@ -4680,16 +4680,16 @@
         <v>49</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="Y28" t="n">
         <v>3.333</v>
@@ -4845,16 +4845,16 @@
         <v>61</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y29" t="n">
         <v>1.333</v>
@@ -5010,16 +5010,16 @@
         <v>42</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="Y30" t="n">
         <v>1.833</v>
@@ -5175,16 +5175,16 @@
         <v>77</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y31" t="n">
         <v>4.833</v>
@@ -5340,16 +5340,16 @@
         <v>158</v>
       </c>
       <c r="U32" t="n">
-        <v>0.833</v>
+        <v>3.333</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>3.333</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.333</v>
       </c>
       <c r="Y32" t="n">
         <v>7</v>
@@ -5511,10 +5511,10 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y33" t="n">
         <v>0.4</v>
@@ -5670,10 +5670,10 @@
         <v>26</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -5835,16 +5835,16 @@
         <v>30</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y35" t="n">
         <v>0.833</v>
@@ -6003,13 +6003,13 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y36" t="n">
         <v>0.667</v>
@@ -6495,16 +6495,16 @@
         <v>664</v>
       </c>
       <c r="U39" t="n">
-        <v>0.833</v>
+        <v>9.833</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>11.833</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>15.333</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y39" t="n">
         <v>29.667</v>
@@ -6660,16 +6660,16 @@
         <v>608</v>
       </c>
       <c r="U40" t="n">
-        <v>1.5</v>
+        <v>6.833</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>7.833</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>4.333</v>
       </c>
       <c r="Y40" t="n">
         <v>26.833</v>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_VALENCIA BASKET.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_VALENCIA BASKET.xlsx
@@ -683,13 +683,13 @@
         <v>61</v>
       </c>
       <c r="N2" t="n">
-        <v>178</v>
+        <v>102</v>
       </c>
       <c r="O2" t="n">
-        <v>215</v>
+        <v>139</v>
       </c>
       <c r="P2" t="n">
-        <v>0.524390243902439</v>
+        <v>0.3390243902439025</v>
       </c>
       <c r="Q2" t="n">
         <v>24</v>
@@ -713,22 +713,22 @@
         <v>10</v>
       </c>
       <c r="X2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.07804878048780488</v>
+        <v>0.08048780487804878</v>
       </c>
       <c r="Z2" t="n">
         <v>51</v>
       </c>
       <c r="AA2" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3829268292682927</v>
+        <v>0.3804878048780488</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.827906976744186</v>
+        <v>0.7338129496402878</v>
       </c>
       <c r="AD2" t="n">
         <v>0.3478260869565217</v>
@@ -737,13 +737,13 @@
         <v>0.4615384615384616</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3125</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3248407643312102</v>
+        <v>0.3269230769230769</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.655813953488372</v>
+        <v>1.467625899280576</v>
       </c>
       <c r="AI2" t="n">
         <v>0.9230769230769231</v>
@@ -813,13 +813,13 @@
         <v>10.16666666666667</v>
       </c>
       <c r="N3" t="n">
-        <v>29.66666666666667</v>
+        <v>17</v>
       </c>
       <c r="O3" t="n">
-        <v>35.83333333333334</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5243902439024389</v>
+        <v>0.3390243902439024</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
@@ -843,22 +843,22 @@
         <v>1.666666666666667</v>
       </c>
       <c r="X3" t="n">
-        <v>5.333333333333333</v>
+        <v>5.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.07804878048780486</v>
+        <v>0.08048780487804877</v>
       </c>
       <c r="Z3" t="n">
         <v>8.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3829268292682926</v>
+        <v>0.3804878048780487</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.827906976744186</v>
+        <v>0.7338129496402878</v>
       </c>
       <c r="AD3" t="n">
         <v>0.3478260869565217</v>
@@ -867,13 +867,13 @@
         <v>0.4615384615384616</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3125000000000001</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3248407643312102</v>
+        <v>0.3269230769230769</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.655813953488372</v>
+        <v>1.467625899280576</v>
       </c>
       <c r="AI3" t="n">
         <v>0.9230769230769231</v>
@@ -943,13 +943,13 @@
         <v>63</v>
       </c>
       <c r="N4" t="n">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="O4" t="n">
-        <v>225</v>
+        <v>147</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5408653846153846</v>
+        <v>0.3533653846153846</v>
       </c>
       <c r="Q4" t="n">
         <v>34</v>
@@ -970,25 +970,25 @@
         <v>0.03846153846153846</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05528846153846154</v>
+        <v>0.0673076923076923</v>
       </c>
       <c r="Z4" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="AA4" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3629807692307692</v>
+        <v>0.3509615384615384</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7155555555555555</v>
+        <v>0.564625850340136</v>
       </c>
       <c r="AD4" t="n">
         <v>0.4303797468354431</v>
@@ -997,13 +997,13 @@
         <v>0.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3841059602649007</v>
+        <v>0.3698630136986301</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.431111111111111</v>
+        <v>1.129251700680272</v>
       </c>
       <c r="AI4" t="n">
         <v>1</v>
@@ -1073,13 +1073,13 @@
         <v>10.5</v>
       </c>
       <c r="N5" t="n">
-        <v>26.83333333333333</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="O5" t="n">
-        <v>37.5</v>
+        <v>24.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5408653846153846</v>
+        <v>0.3533653846153846</v>
       </c>
       <c r="Q5" t="n">
         <v>5.666666666666667</v>
@@ -1100,25 +1100,25 @@
         <v>0.03846153846153846</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>3.833333333333333</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05528846153846154</v>
+        <v>0.0673076923076923</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.666666666666666</v>
+        <v>9</v>
       </c>
       <c r="AA5" t="n">
-        <v>25.16666666666667</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3629807692307692</v>
+        <v>0.3509615384615384</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7155555555555555</v>
+        <v>0.5646258503401361</v>
       </c>
       <c r="AD5" t="n">
         <v>0.4303797468354431</v>
@@ -1127,13 +1127,13 @@
         <v>0.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.3214285714285714</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3841059602649006</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.431111111111111</v>
+        <v>1.129251700680272</v>
       </c>
       <c r="AI5" t="n">
         <v>1</v>
@@ -1498,13 +1498,13 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.806</v>
+        <v>0.647</v>
       </c>
       <c r="AB8" t="n">
         <v>4</v>
@@ -1663,13 +1663,13 @@
         <v>6</v>
       </c>
       <c r="Y9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Z9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.741</v>
+        <v>0.696</v>
       </c>
       <c r="AB9" t="n">
         <v>5</v>
@@ -1993,13 +1993,13 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.909</v>
+        <v>0.846</v>
       </c>
       <c r="AB11" t="n">
         <v>1</v>
@@ -2158,13 +2158,13 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z12" t="n">
         <v>8</v>
       </c>
-      <c r="Z12" t="n">
-        <v>9</v>
-      </c>
       <c r="AA12" t="n">
-        <v>0.889</v>
+        <v>0.875</v>
       </c>
       <c r="AB12" t="n">
         <v>1</v>
@@ -2323,13 +2323,13 @@
         <v>4</v>
       </c>
       <c r="Y13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.917</v>
+        <v>0.833</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2353,19 +2353,19 @@
         <v>4</v>
       </c>
       <c r="AI13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AK13" t="n">
         <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
@@ -2488,13 +2488,13 @@
         <v>9</v>
       </c>
       <c r="Y14" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="Z14" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.829</v>
+        <v>0.76</v>
       </c>
       <c r="AB14" t="n">
         <v>5</v>
@@ -2653,13 +2653,13 @@
         <v>14</v>
       </c>
       <c r="Y15" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="Z15" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="AB15" t="n">
         <v>3</v>
@@ -2818,13 +2818,13 @@
         <v>1</v>
       </c>
       <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
         <v>2</v>
       </c>
-      <c r="Z16" t="n">
-        <v>4</v>
-      </c>
       <c r="AA16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>1</v>
@@ -2983,13 +2983,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.667</v>
+        <v>0.643</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -3148,13 +3148,13 @@
         <v>2</v>
       </c>
       <c r="Y18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.833</v>
+        <v>0.667</v>
       </c>
       <c r="AB18" t="n">
         <v>3</v>
@@ -3313,13 +3313,13 @@
         <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="AB19" t="n">
         <v>1</v>
@@ -3808,13 +3808,13 @@
         <v>54</v>
       </c>
       <c r="Y22" t="n">
-        <v>178</v>
+        <v>102</v>
       </c>
       <c r="Z22" t="n">
-        <v>215</v>
+        <v>139</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.828</v>
+        <v>0.734</v>
       </c>
       <c r="AB22" t="n">
         <v>24</v>
@@ -3838,19 +3838,19 @@
         <v>10</v>
       </c>
       <c r="AI22" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.312</v>
+        <v>0.303</v>
       </c>
       <c r="AK22" t="n">
         <v>51</v>
       </c>
       <c r="AL22" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.325</v>
+        <v>0.327</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
@@ -3973,13 +3973,13 @@
         <v>26</v>
       </c>
       <c r="Y23" t="n">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="Z23" t="n">
-        <v>225</v>
+        <v>147</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.716</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AB23" t="n">
         <v>34</v>
@@ -4000,22 +4000,22 @@
         <v>0.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AI23" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.217</v>
+        <v>0.321</v>
       </c>
       <c r="AK23" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="AL23" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.384</v>
+        <v>0.37</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
@@ -4197,13 +4197,13 @@
         <v>1.333</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.167</v>
+        <v>1.833</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.167</v>
+        <v>2.833</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.806</v>
+        <v>0.647</v>
       </c>
       <c r="AB25" t="n">
         <v>0.667</v>
@@ -4362,13 +4362,13 @@
         <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.333</v>
+        <v>2.667</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.5</v>
+        <v>3.833</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.741</v>
+        <v>0.696</v>
       </c>
       <c r="AB26" t="n">
         <v>0.833</v>
@@ -4692,13 +4692,13 @@
         <v>0.833</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.333</v>
+        <v>1.833</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.667</v>
+        <v>2.167</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.909</v>
+        <v>0.846</v>
       </c>
       <c r="AB28" t="n">
         <v>0.167</v>
@@ -4857,13 +4857,13 @@
         <v>0.167</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="Z29" t="n">
         <v>1.333</v>
       </c>
-      <c r="Z29" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA29" t="n">
-        <v>0.889</v>
+        <v>0.875</v>
       </c>
       <c r="AB29" t="n">
         <v>0.167</v>
@@ -5022,13 +5022,13 @@
         <v>0.667</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.833</v>
+        <v>0.833</v>
       </c>
       <c r="Z30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.917</v>
+        <v>0.833</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0.667</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.667</v>
+        <v>0.833</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AK30" t="n">
         <v>0.5</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
@@ -5187,13 +5187,13 @@
         <v>1.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.833</v>
+        <v>3.167</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.833</v>
+        <v>4.167</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.829</v>
+        <v>0.76</v>
       </c>
       <c r="AB31" t="n">
         <v>0.833</v>
@@ -5352,13 +5352,13 @@
         <v>2.333</v>
       </c>
       <c r="Y32" t="n">
-        <v>7</v>
+        <v>2.833</v>
       </c>
       <c r="Z32" t="n">
-        <v>7.5</v>
+        <v>3.333</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="AB32" t="n">
         <v>0.5</v>
@@ -5517,13 +5517,13 @@
         <v>0.2</v>
       </c>
       <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
         <v>0.4</v>
       </c>
-      <c r="Z33" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AA33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0.2</v>
@@ -5682,13 +5682,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.667</v>
+        <v>1.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.5</v>
+        <v>2.333</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.667</v>
+        <v>0.643</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -5847,13 +5847,13 @@
         <v>0.333</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.833</v>
+        <v>0.333</v>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.833</v>
+        <v>0.667</v>
       </c>
       <c r="AB35" t="n">
         <v>0.5</v>
@@ -6012,13 +6012,13 @@
         <v>0.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.167</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="AB36" t="n">
         <v>0.167</v>
@@ -6507,13 +6507,13 @@
         <v>9</v>
       </c>
       <c r="Y39" t="n">
-        <v>29.667</v>
+        <v>17</v>
       </c>
       <c r="Z39" t="n">
-        <v>35.833</v>
+        <v>23.167</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.828</v>
+        <v>0.734</v>
       </c>
       <c r="AB39" t="n">
         <v>4</v>
@@ -6537,19 +6537,19 @@
         <v>1.667</v>
       </c>
       <c r="AI39" t="n">
-        <v>5.333</v>
+        <v>5.5</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.313</v>
+        <v>0.303</v>
       </c>
       <c r="AK39" t="n">
         <v>8.5</v>
       </c>
       <c r="AL39" t="n">
-        <v>26.167</v>
+        <v>26</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.325</v>
+        <v>0.327</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
@@ -6672,13 +6672,13 @@
         <v>4.333</v>
       </c>
       <c r="Y40" t="n">
-        <v>26.833</v>
+        <v>13.833</v>
       </c>
       <c r="Z40" t="n">
-        <v>37.5</v>
+        <v>24.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.716</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AB40" t="n">
         <v>5.667</v>
@@ -6699,22 +6699,22 @@
         <v>0.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.833</v>
+        <v>1.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>3.833</v>
+        <v>4.667</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.217</v>
+        <v>0.321</v>
       </c>
       <c r="AK40" t="n">
-        <v>9.667</v>
+        <v>9</v>
       </c>
       <c r="AL40" t="n">
-        <v>25.167</v>
+        <v>24.333</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.384</v>
+        <v>0.37</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
